--- a/nriss-patch-1/ig/CodeSystem-terminologie-minimal-ruim.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-terminologie-minimal-ruim.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:12:34+00:00</t>
+    <t>2026-03-27T13:20:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-terminologie-minimal-ruim.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-terminologie-minimal-ruim.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T13:20:16+00:00</t>
+    <t>2026-03-30T07:06:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-terminologie-minimal-ruim.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-terminologie-minimal-ruim.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:06:10+00:00</t>
+    <t>2026-03-30T07:17:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nriss-patch-1/ig/CodeSystem-terminologie-minimal-ruim.xlsx
+++ b/nriss-patch-1/ig/CodeSystem-terminologie-minimal-ruim.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:17:30+00:00</t>
+    <t>2026-03-30T07:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
